--- a/docs/006_マネークエスト_追加機能テスト仕様書_v1.0.xlsx
+++ b/docs/006_マネークエスト_追加機能テスト仕様書_v1.0.xlsx
@@ -624,7 +624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:G31"/>
+  <dimension ref="B1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -715,7 +715,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>v1.1</t>
+          <t>v1.2</t>
         </is>
       </c>
     </row>
@@ -835,6 +835,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
@@ -902,20 +903,79 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="B33" s="25" t="inlineStr">
+        <is>
+          <t>修正後再確認サマリー(v1.2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="B34" s="25" t="inlineStr">
+        <is>
+          <t>再確認日</t>
+        </is>
+      </c>
+      <c r="D34" s="26" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="B35" s="25" t="inlineStr">
+        <is>
+          <t>総件数 / OK数 / NG数</t>
+        </is>
+      </c>
+      <c r="D35" s="26" t="inlineStr">
+        <is>
+          <t>65 / 65 / 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="B36" s="25" t="inlineStr">
+        <is>
+          <t>修正1</t>
+        </is>
+      </c>
+      <c r="D36" s="26" t="inlineStr">
+        <is>
+          <t>HomeController#updateCharacterTypeに@Valid+BindingResultチェックを追加(HTTP500→正常リダイレクト)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="B37" s="25" t="inlineStr">
+        <is>
+          <t>修正2</t>
+        </is>
+      </c>
+      <c r="D37" s="26" t="inlineStr">
+        <is>
+          <t>parent-home.htmlのクエスト一覧に「じっしできる曜日」「じっしび」の表示を追加</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="18">
     <mergeCell ref="D31:G31"/>
     <mergeCell ref="D9:G9"/>
     <mergeCell ref="D3:G3"/>
+    <mergeCell ref="D35:G35"/>
+    <mergeCell ref="D36:G36"/>
     <mergeCell ref="D8:G8"/>
     <mergeCell ref="D6:G6"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="D7:G7"/>
     <mergeCell ref="D30:G30"/>
     <mergeCell ref="D27:G27"/>
+    <mergeCell ref="D34:G34"/>
     <mergeCell ref="D29:G29"/>
     <mergeCell ref="B12:G13"/>
     <mergeCell ref="D5:G5"/>
+    <mergeCell ref="D37:G37"/>
     <mergeCell ref="D28:G28"/>
     <mergeCell ref="D4:G4"/>
   </mergeCells>
@@ -929,7 +989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -989,6 +1049,22 @@
       <c r="D3" s="27" t="inlineStr">
         <is>
           <t>追加機能5シート(計65件)のテストを実施し、結果(OK63件/NG2件)を記録</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>v1.2</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="n">
+        <v>46217</v>
+      </c>
+      <c r="C4" s="27" t="inlineStr"/>
+      <c r="D4" s="27" t="inlineStr">
+        <is>
+          <t>テストで見つかったNG2件(キャラクター種類未指定時のHTTP500、保護者側クエスト一覧の曜日/特定日未表示)を修正し、再確認して全件OKに更新</t>
         </is>
       </c>
     </row>
@@ -2321,10 +2397,10 @@
         <v>11</v>
       </c>
       <c r="D3" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="12" t="n">
         <v>0</v>
@@ -3360,7 +3436,7 @@
       </c>
       <c r="N17" s="15" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="O17" s="23" t="n">
@@ -3376,7 +3452,8 @@
       <c r="S17" s="15" t="inlineStr">
         <is>
           <t>サーバー側に@Validが付与されていないため、実際にはエラーにならず種類がnullで保存される可能性がある。実施結果を要確認
-characterType未指定でPOSTするとHTTP 500(内部エラー)が発生し、「キャラクターのしゅるいを選んでください」等の想定していたエラーメッセージは表示されない。/child/character/type に@Validが付与されておらずサーバー側バリデーションが効いていないため。ただしDBのNOT NULL制約により実際にはキャラクター種類は変更されず、データ破損はない。</t>
+characterType未指定でPOSTするとHTTP 500(内部エラー)が発生し、「キャラクターのしゅるいを選んでください」等の想定していたエラーメッセージは表示されない。/child/character/type に@Validが付与されておらずサーバー側バリデーションが効いていないため。ただしDBのNOT NULL制約により実際にはキャラクター種類は変更されず、データ破損はない。
+[修正確認 2026-07-14] HomeController#updateCharacterTypeに@Valid+BindingResultチェックを追加。characterType未指定でPOSTしても500エラーにならず、/child/homeへ正常リダイレクトされ、キャラクター種類も変更されないことを再確認した。</t>
         </is>
       </c>
     </row>
@@ -3473,10 +3550,10 @@
         <v>16</v>
       </c>
       <c r="D3" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="12" t="n">
         <v>0</v>
@@ -4932,7 +5009,7 @@
       </c>
       <c r="N22" s="15" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="O22" s="23" t="n">
@@ -4947,7 +5024,8 @@
       <c r="R22" s="15" t="n"/>
       <c r="S22" s="15" t="inlineStr">
         <is>
-          <t>保護者のクエスト一覧(parent-home.html)には「じっしできる曜日」「じっしび」の情報が一切表示されない(編集モーダル復元用のdata属性としてのみ保持されている)。子供側の一覧には正しく表示される。</t>
+          <t>保護者のクエスト一覧(parent-home.html)には「じっしできる曜日」「じっしび」の情報が一切表示されない(編集モーダル復元用のdata属性としてのみ保持されている)。子供側の一覧には正しく表示される。
+[修正確認 2026-07-14] parent-home.htmlのクエスト一覧に「じっしできる曜日」「じっしび」の表示を追加。既存クエスト(quest_id=18 ate: 水曜/2026-07-09指定)で保護者側一覧にも正しく表示されることを再確認した。上限承認クエスト(limitAmount != null)には表示されない(意図通り)。</t>
         </is>
       </c>
     </row>
